--- a/energy/DS-1W複合音.xlsx
+++ b/energy/DS-1W複合音.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\recording_application\energy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE755807-C78D-44FF-9392-6441A4532390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C679E6DF-7F46-4544-A7C4-5D470019DA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1420,18 +1420,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>5.3442283887574003E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>1.2629538654812341E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>3.2128105475158923E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>6.6423778555502744E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>0.15920238185600841</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>0.12353828094004531</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>0.30846814302816639</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>1.297879627654922E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>3.3245488703926823E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>6.6169871456932344E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>0.16826766476630961</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>0.12613968402158041</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>0.32685343138046058</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>2.3864090369240819E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>6.2352343649026518E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>0.1260793417689296</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>0.31538198856977651</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>0.24028030843072601</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
